--- a/Sequences/Oligos.xlsx
+++ b/Sequences/Oligos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob-my.sharepoint.com/personal/zw24976_bristol_ac_uk/Documents/Documents/BCL/PhagePol_Terminators/Project Report/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob-my.sharepoint.com/personal/zw24976_bristol_ac_uk/Documents/Documents/GitHub/EngBioCDT-SRP1/Sequences/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_F25DC773A252ABDACC104889F15E741E5BDE58F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D8E6962-B178-47BB-A2CB-04A2D355F993}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="11_F25DC773A252ABDACC104889F15E741E5BDE58F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AFD8AA3-866E-46E5-93B2-D9883FA81345}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,213 +27,108 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="79">
   <si>
-    <t>FXB028_F_J23105_BsaI_GCTT</t>
-  </si>
-  <si>
     <t>AAAggtctcAgcttGGAGttGTCTTCtttacggc</t>
   </si>
   <si>
-    <t>FXB029_F_pSHNJ200_BsaI_F</t>
-  </si>
-  <si>
     <t>AAAggtctcAcgctAAGTCTTCaggtgcttcctcgctc</t>
   </si>
   <si>
-    <t>FXB030_R_SHJN200_BsaI_A</t>
-  </si>
-  <si>
     <t>AAAggtctcActccAAGTCTTCAGTTAGGGACTTATCAAGCGAATTC</t>
   </si>
   <si>
-    <t>FXB031_F_pSHNJ200_BsaBbs</t>
-  </si>
-  <si>
     <t>AAAgaagacAActccagcgGGTCTCaCGCTaggtgcttcctcgctc</t>
   </si>
   <si>
-    <t>FXB032_R_pSHNJ200_BsaBbs</t>
-  </si>
-  <si>
     <t>AAAgaagacAAcgctGGTCTCaCTCCAGTTAGGGACTTATCAAGCGAATTC</t>
   </si>
   <si>
-    <t>FXB033_F_col_pSHNJ200</t>
-  </si>
-  <si>
     <t>aatgtacatcagagattttgagacac</t>
   </si>
   <si>
-    <t>FXB034_R_col_gfasPurple</t>
-  </si>
-  <si>
     <t>caaatcggtggttgcctg</t>
   </si>
   <si>
-    <t>FXB035_F_A_TT7hyb1</t>
-  </si>
-  <si>
     <t>ggagAAACAGATAGGCCCTCttcgGAGGGCCtatctgttTTTTTTT</t>
   </si>
   <si>
-    <t>FXB036_R_E_TT7hyb1</t>
-  </si>
-  <si>
     <t>aagcAAAAAAAaacagataGGCCCTCcgaaGAGGGCCTATCTGTTT</t>
   </si>
   <si>
-    <t>FXB037_F_A_TT7hyb8</t>
-  </si>
-  <si>
     <t>ggagTAAAGAATAAACCttcgGGTTTATTCTTTAGTTTTTTTT</t>
   </si>
   <si>
-    <t>FXB038_R_E_TT7hyb8</t>
-  </si>
-  <si>
     <t>aagcAAAAAAAACTAAAGAATAAACCcgaaGGTTTATTCTTTA</t>
   </si>
   <si>
-    <t>FXB039_F_A_L3S2P11</t>
-  </si>
-  <si>
     <t>ggagCTCGGTACCAAATTCCAGAAAAGAGACGCTTTCGAGCGTCTTTTTTCGTTTTGGTC</t>
   </si>
   <si>
-    <t>FXB040_R_E_L3S2P11</t>
-  </si>
-  <si>
     <t>aagcGACCAAAACGAAAAAAGACGCTCGAAAGCGTCTCTTTTCTGGAATTTGGTACCGAG</t>
   </si>
   <si>
-    <t>FXB041_F_A_L3S1P00</t>
-  </si>
-  <si>
     <t>ggagGACGAACAATAAGGGGAGCGGGAAACCGCTCCCCTTTTTTATTGATAACAAAA</t>
   </si>
   <si>
-    <t>FXB042_R_E_L3S1P00</t>
-  </si>
-  <si>
     <t>aagcTTTTGTTATCAATAAAAAAGGGGAGCGGTTTCCCGCTCCCCTTATTGTTCGTC</t>
   </si>
   <si>
-    <t>FXB043_F_A_50spacer</t>
-  </si>
-  <si>
     <t>ggagCGCTTAACGGCTCCTTACCCGCTTTGCGTTACCTTGCAGGAATCGAGGCC</t>
   </si>
   <si>
-    <t>FXB044_R_E_50spacer</t>
-  </si>
-  <si>
     <t>aagcGGCCTCGATTCCTGCAAGGTAACGCAAAGCGGGTAAGGAGCCGTTAAGCG</t>
   </si>
   <si>
-    <t>FXB045_F_BbsI_E_lacO</t>
-  </si>
-  <si>
     <t>AAAGAAGACAAgcttAATTGTGAGCGCTCACAATT</t>
   </si>
   <si>
-    <t>FXB046_R_B_lacO</t>
-  </si>
-  <si>
     <t>agtaAATTGTGAGCGCTCACAATTaagcTTGTCTTCTTT</t>
   </si>
   <si>
-    <t>FXB047_F_BbsI_E_tetO</t>
-  </si>
-  <si>
     <t>AAAGAAGACAAgcttTCCCTATCAGTGATAGAGA</t>
   </si>
   <si>
-    <t>FXB048_R_B_tetO</t>
-  </si>
-  <si>
     <t>agtaTCTCTATCACTGATAGGGAaagcTTGTCTTCTTT</t>
   </si>
   <si>
-    <t>FXB049_F_BbsI_E_G3T</t>
-  </si>
-  <si>
     <t>AAAGAAGACAAgcttGGGTGGGTGGGTGGG</t>
   </si>
   <si>
-    <t>FXB050_R_B_G3T</t>
-  </si>
-  <si>
     <t>agtaCCCACCCACCCACCCaagcTTGTCTTCTTT</t>
   </si>
   <si>
-    <t>FXB051_F_BbsI_E_G3Trev</t>
-  </si>
-  <si>
     <t>AAAGAAGACAAgcttCCCACCCACCCACCC</t>
   </si>
   <si>
-    <t>FXB052_R_B_G3Trev</t>
-  </si>
-  <si>
     <t>agtaGGGTGGGTGGGTGGGaagcTTGTCTTCTTT</t>
   </si>
   <si>
-    <t>FXB053_F_BbsI_E_20spacer</t>
-  </si>
-  <si>
     <t>AAAGAAGACAAgcttTATCGGAGCGCCTCCGTACA</t>
   </si>
   <si>
-    <t>FXB054_R_B_20spacer</t>
-  </si>
-  <si>
     <t>agtaTGTACGGAGGCGCTCCGATAaagcTTGTCTTCTTT</t>
   </si>
   <si>
-    <t>FXB055_F_BbsI_E_20_lacO</t>
-  </si>
-  <si>
     <t>AAAGAAGACAAgcttTATCGGAGCGCCTCCGTACAAATTGTGAGCGCTCACAATT</t>
   </si>
   <si>
-    <t>FXB056_R_B_20_lacO</t>
-  </si>
-  <si>
     <t>agtaAATTGTGAGCGCTCACAATTTGTACGGAGGCGCTCCGATAaagcTTGTCTTCTTT</t>
   </si>
   <si>
-    <t>FXB057_F_BbsI_E_20_tetO</t>
-  </si>
-  <si>
     <t>AAAGAAGACAAgcttTATCGGAGCGCCTCCGTACATCCCTATCAGTGATAGAGA</t>
   </si>
   <si>
-    <t>FXB058_R_B_20_tetO</t>
-  </si>
-  <si>
     <t>agtaTCTCTATCACTGATAGGGATGTACGGAGGCGCTCCGATAaagcTTGTCTTCTTT</t>
   </si>
   <si>
-    <t>FXB059_F_BbsI_E_20_G3T</t>
-  </si>
-  <si>
     <t>AAAGAAGACAAgcttTATCGGAGCGCCTCCGTACAGGGTGGGTGGGTGGG</t>
   </si>
   <si>
-    <t>FXB060_R_B_20_G3T</t>
-  </si>
-  <si>
     <t>agtaCCCACCCACCCACCCTGTACGGAGGCGCTCCGATAaagcTTGTCTTCTTT</t>
   </si>
   <si>
-    <t>FXB061_F_BbsI_E_20_G3Trev</t>
-  </si>
-  <si>
     <t>AAAGAAGACAAgcttTATCGGAGCGCCTCCGTACACCCACCCACCCACCC</t>
   </si>
   <si>
-    <t>FXB062_R_B_20_G3Trev</t>
-  </si>
-  <si>
     <t>agtaGGGTGGGTGGGTGGGTGTACGGAGGCGCTCCGATAaagcTTGTCTTCTTT</t>
   </si>
   <si>
@@ -243,25 +138,130 @@
     <t>Sequence</t>
   </si>
   <si>
-    <t>FXB015_A_noTer</t>
-  </si>
-  <si>
     <t>ggagGCCATACTCGTCCGCGGAGC</t>
   </si>
   <si>
-    <t>FXB016_B_noTer</t>
-  </si>
-  <si>
     <t>agtaGCTCCGCGGACGAGTATGGC</t>
   </si>
   <si>
-    <t>FXB017_A_TT7hyb1</t>
-  </si>
-  <si>
-    <t>FXB018_B_TT7hyb1</t>
-  </si>
-  <si>
     <t>agtaAAAAAAAaacagataGGCCCTCcgaaGAGGGCCTATCTGTTT</t>
+  </si>
+  <si>
+    <t>oFXB015_A_noTer</t>
+  </si>
+  <si>
+    <t>oFXB016_B_noTer</t>
+  </si>
+  <si>
+    <t>oFXB017_A_TT7hyb1</t>
+  </si>
+  <si>
+    <t>oFXB018_B_TT7hyb1</t>
+  </si>
+  <si>
+    <t>oFXB028_F_J23105_BsaI_GCTT</t>
+  </si>
+  <si>
+    <t>oFXB029_F_pSHNJ200_BsaI_F</t>
+  </si>
+  <si>
+    <t>oFXB030_R_SHJN200_BsaI_A</t>
+  </si>
+  <si>
+    <t>oFXB062_R_B_20_G3Trev</t>
+  </si>
+  <si>
+    <t>oFXB031_F_pSHNJ200_BsaBbs</t>
+  </si>
+  <si>
+    <t>oFXB032_R_pSHNJ200_BsaBbs</t>
+  </si>
+  <si>
+    <t>oFXB033_F_col_pSHNJ200</t>
+  </si>
+  <si>
+    <t>oFXB034_R_col_gfasPurple</t>
+  </si>
+  <si>
+    <t>oFXB035_F_A_TT7hyb1</t>
+  </si>
+  <si>
+    <t>oFXB036_R_E_TT7hyb1</t>
+  </si>
+  <si>
+    <t>oFXB037_F_A_TT7hyb8</t>
+  </si>
+  <si>
+    <t>oFXB038_R_E_TT7hyb8</t>
+  </si>
+  <si>
+    <t>oFXB039_F_A_L3S2P11</t>
+  </si>
+  <si>
+    <t>oFXB040_R_E_L3S2P11</t>
+  </si>
+  <si>
+    <t>oFXB041_F_A_L3S1P00</t>
+  </si>
+  <si>
+    <t>oFXB042_R_E_L3S1P00</t>
+  </si>
+  <si>
+    <t>oFXB043_F_A_50spacer</t>
+  </si>
+  <si>
+    <t>oFXB044_R_E_50spacer</t>
+  </si>
+  <si>
+    <t>oFXB045_F_BbsI_E_lacO</t>
+  </si>
+  <si>
+    <t>oFXB046_R_B_lacO</t>
+  </si>
+  <si>
+    <t>oFXB047_F_BbsI_E_tetO</t>
+  </si>
+  <si>
+    <t>oFXB048_R_B_tetO</t>
+  </si>
+  <si>
+    <t>oFXB049_F_BbsI_E_G3T</t>
+  </si>
+  <si>
+    <t>oFXB050_R_B_G3T</t>
+  </si>
+  <si>
+    <t>oFXB051_F_BbsI_E_G3Trev</t>
+  </si>
+  <si>
+    <t>oFXB052_R_B_G3Trev</t>
+  </si>
+  <si>
+    <t>oFXB053_F_BbsI_E_20spacer</t>
+  </si>
+  <si>
+    <t>oFXB054_R_B_20spacer</t>
+  </si>
+  <si>
+    <t>oFXB055_F_BbsI_E_20_lacO</t>
+  </si>
+  <si>
+    <t>oFXB056_R_B_20_lacO</t>
+  </si>
+  <si>
+    <t>oFXB057_F_BbsI_E_20_tetO</t>
+  </si>
+  <si>
+    <t>oFXB058_R_B_20_tetO</t>
+  </si>
+  <si>
+    <t>oFXB059_F_BbsI_E_20_G3T</t>
+  </si>
+  <si>
+    <t>oFXB060_R_B_20_G3T</t>
+  </si>
+  <si>
+    <t>oFXB061_F_BbsI_E_20_G3Trev</t>
   </si>
 </sst>
 </file>
@@ -304,9 +304,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -591,327 +590,327 @@
   <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="25.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B33" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="B34" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B35" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="B36" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="B37" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B38" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="B39" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" t="s">
         <v>34</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>
